--- a/docs/relatorio_meteoro.xlsx
+++ b/docs/relatorio_meteoro.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="171">
   <si>
     <t>data_hora</t>
   </si>
@@ -103,433 +103,427 @@
     <t>amostra</t>
   </si>
   <si>
+    <t>1.0928</t>
+  </si>
+  <si>
+    <t>968.2</t>
+  </si>
+  <si>
+    <t>1.0929</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>968.5</t>
+  </si>
+  <si>
+    <t>10.95</t>
+  </si>
+  <si>
+    <t>1.0938</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>1.0935</t>
+  </si>
+  <si>
+    <t>968.6</t>
+  </si>
+  <si>
+    <t>1.0925</t>
+  </si>
+  <si>
+    <t>10.75</t>
+  </si>
+  <si>
+    <t>967.5</t>
+  </si>
+  <si>
+    <t>1.0911</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>1.0903</t>
+  </si>
+  <si>
+    <t>966.5</t>
+  </si>
+  <si>
+    <t>1.0901</t>
+  </si>
+  <si>
+    <t>966.4</t>
+  </si>
+  <si>
+    <t>1.0893</t>
+  </si>
+  <si>
+    <t>966.1</t>
+  </si>
+  <si>
+    <t>1.0877</t>
+  </si>
+  <si>
     <t>0.4</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>965.9</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>1.0867</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>1.61</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>1.0862</t>
+  </si>
+  <si>
+    <t>ENE</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>32.2</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>10.19</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>1.0864</t>
+  </si>
+  <si>
+    <t>32.8</t>
+  </si>
+  <si>
+    <t>15.35</t>
+  </si>
+  <si>
+    <t>1.0861</t>
+  </si>
+  <si>
+    <t>33.1</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>966.2</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>31.4</t>
+  </si>
+  <si>
+    <t>966.3</t>
+  </si>
+  <si>
+    <t>22.66</t>
+  </si>
+  <si>
+    <t>1.0853</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>32.9</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>1.0854</t>
+  </si>
+  <si>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>35.65</t>
+  </si>
+  <si>
+    <t>10.55</t>
+  </si>
+  <si>
+    <t>1.0865</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>966.6</t>
+  </si>
+  <si>
+    <t>34.88</t>
+  </si>
+  <si>
+    <t>1.0868</t>
+  </si>
+  <si>
+    <t>ESE</t>
+  </si>
+  <si>
+    <t>966.9</t>
+  </si>
+  <si>
+    <t>35.09</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>1.0874</t>
+  </si>
+  <si>
+    <t>967.3</t>
+  </si>
+  <si>
+    <t>41.07</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>967.6</t>
+  </si>
+  <si>
+    <t>45.03</t>
+  </si>
+  <si>
+    <t>1.0886</t>
+  </si>
+  <si>
+    <t>968.1</t>
+  </si>
+  <si>
+    <t>45.41</t>
+  </si>
+  <si>
+    <t>1.0897</t>
+  </si>
+  <si>
+    <t>968.8</t>
+  </si>
+  <si>
+    <t>46.58</t>
+  </si>
+  <si>
+    <t>11.28</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>969.2</t>
+  </si>
+  <si>
+    <t>28.13</t>
+  </si>
+  <si>
+    <t>1.0913</t>
+  </si>
+  <si>
+    <t>969.6</t>
+  </si>
+  <si>
+    <t>35.74</t>
+  </si>
+  <si>
+    <t>1.0918</t>
+  </si>
+  <si>
+    <t>4.83</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>27.14</t>
+  </si>
+  <si>
+    <t>11.29</t>
+  </si>
+  <si>
+    <t>1.0927</t>
+  </si>
+  <si>
+    <t>969.7</t>
+  </si>
+  <si>
+    <t>29.67</t>
+  </si>
+  <si>
+    <t>1.0934</t>
+  </si>
+  <si>
     <t>NE</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>968.4</t>
-  </si>
-  <si>
-    <t>13.92</t>
-  </si>
-  <si>
-    <t>1.0915</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>1.0912</t>
-  </si>
-  <si>
-    <t>968.6</t>
-  </si>
-  <si>
-    <t>13.62</t>
-  </si>
-  <si>
-    <t>1.0916</t>
-  </si>
-  <si>
-    <t>1.0917</t>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>969.9</t>
+  </si>
+  <si>
+    <t>26.88</t>
+  </si>
+  <si>
+    <t>11.71</t>
+  </si>
+  <si>
+    <t>18.23</t>
+  </si>
+  <si>
+    <t>11.92</t>
+  </si>
+  <si>
+    <t>1.0962</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>19.35</t>
+  </si>
+  <si>
+    <t>11.93</t>
+  </si>
+  <si>
+    <t>1.0979</t>
+  </si>
+  <si>
+    <t>8.47</t>
+  </si>
+  <si>
+    <t>12.53</t>
+  </si>
+  <si>
+    <t>1.0982</t>
+  </si>
+  <si>
+    <t>969.4</t>
+  </si>
+  <si>
+    <t>4.26</t>
+  </si>
+  <si>
+    <t>12.55</t>
+  </si>
+  <si>
+    <t>1.0987</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>12.86</t>
+  </si>
+  <si>
+    <t>1.0988</t>
   </si>
   <si>
     <t>968.3</t>
   </si>
   <si>
-    <t>13.61</t>
-  </si>
-  <si>
-    <t>1.0906</t>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>1.0985</t>
+  </si>
+  <si>
+    <t>12.85</t>
+  </si>
+  <si>
+    <t>1.0976</t>
+  </si>
+  <si>
+    <t>1.0971</t>
+  </si>
+  <si>
+    <t>967.9</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>12.83</t>
+  </si>
+  <si>
+    <t>1.0959</t>
   </si>
   <si>
     <t>967.7</t>
   </si>
   <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>1.0903</t>
-  </si>
-  <si>
-    <t>1.0892</t>
-  </si>
-  <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>966.4</t>
-  </si>
-  <si>
-    <t>1.0885</t>
-  </si>
-  <si>
-    <t>965.8</t>
-  </si>
-  <si>
-    <t>13.25</t>
-  </si>
-  <si>
-    <t>1.0879</t>
-  </si>
-  <si>
-    <t>1.61</t>
-  </si>
-  <si>
-    <t>965.3</t>
-  </si>
-  <si>
-    <t>0.16</t>
-  </si>
-  <si>
-    <t>12.96</t>
-  </si>
-  <si>
-    <t>1.0865</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>965.5</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>12.71</t>
-  </si>
-  <si>
-    <t>1.0869</t>
-  </si>
-  <si>
-    <t>2.41</t>
-  </si>
-  <si>
-    <t>965.1</t>
-  </si>
-  <si>
-    <t>2.62</t>
-  </si>
-  <si>
-    <t>1.0867</t>
-  </si>
-  <si>
-    <t>NNE</t>
-  </si>
-  <si>
-    <t>3.22</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>4.86</t>
-  </si>
-  <si>
-    <t>11.69</t>
-  </si>
-  <si>
-    <t>1.0864</t>
-  </si>
-  <si>
-    <t>33.7</t>
-  </si>
-  <si>
-    <t>1.0838</t>
-  </si>
-  <si>
-    <t>ENE</t>
-  </si>
-  <si>
-    <t>33.3</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>964.5</t>
-  </si>
-  <si>
-    <t>23.65</t>
-  </si>
-  <si>
-    <t>1.0833</t>
-  </si>
-  <si>
-    <t>33.2</t>
-  </si>
-  <si>
-    <t>32.8</t>
-  </si>
-  <si>
-    <t>1.0812</t>
-  </si>
-  <si>
-    <t>32.3</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>965.6</t>
-  </si>
-  <si>
-    <t>20.77</t>
-  </si>
-  <si>
-    <t>12.38</t>
-  </si>
-  <si>
-    <t>32.7</t>
-  </si>
-  <si>
-    <t>966.1</t>
-  </si>
-  <si>
-    <t>32.81</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>12.37</t>
-  </si>
-  <si>
-    <t>1.0814</t>
-  </si>
-  <si>
-    <t>31.9</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>34.02</t>
-  </si>
-  <si>
-    <t>12.25</t>
-  </si>
-  <si>
-    <t>1.0817</t>
-  </si>
-  <si>
-    <t>966.9</t>
-  </si>
-  <si>
-    <t>12.26</t>
-  </si>
-  <si>
-    <t>1.0828</t>
-  </si>
-  <si>
-    <t>967.5</t>
-  </si>
-  <si>
-    <t>29.93</t>
-  </si>
-  <si>
-    <t>32.6</t>
-  </si>
-  <si>
-    <t>12.27</t>
-  </si>
-  <si>
-    <t>1.0847</t>
-  </si>
-  <si>
-    <t>25.42</t>
-  </si>
-  <si>
-    <t>32.2</t>
-  </si>
-  <si>
-    <t>1.0862</t>
-  </si>
-  <si>
-    <t>12.28</t>
-  </si>
-  <si>
-    <t>1.0875</t>
-  </si>
-  <si>
-    <t>969.2</t>
-  </si>
-  <si>
-    <t>22.71</t>
-  </si>
-  <si>
-    <t>31.6</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>969.6</t>
-  </si>
-  <si>
-    <t>23.18</t>
-  </si>
-  <si>
-    <t>12.29</t>
-  </si>
-  <si>
-    <t>1.0905</t>
-  </si>
-  <si>
-    <t>969.8</t>
-  </si>
-  <si>
-    <t>21.76</t>
-  </si>
-  <si>
-    <t>12.44</t>
-  </si>
-  <si>
-    <t>1.0914</t>
-  </si>
-  <si>
-    <t>969.7</t>
-  </si>
-  <si>
-    <t>28.25</t>
-  </si>
-  <si>
-    <t>12.46</t>
-  </si>
-  <si>
-    <t>1.0928</t>
-  </si>
-  <si>
-    <t>WSW</t>
-  </si>
-  <si>
-    <t>21.98</t>
-  </si>
-  <si>
-    <t>12.78</t>
-  </si>
-  <si>
     <t>1.0954</t>
   </si>
   <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>11.44</t>
-  </si>
-  <si>
-    <t>1.0974</t>
-  </si>
-  <si>
-    <t>1.0978</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>7.18</t>
-  </si>
-  <si>
-    <t>13.26</t>
-  </si>
-  <si>
-    <t>1.0982</t>
-  </si>
-  <si>
-    <t>968.2</t>
-  </si>
-  <si>
-    <t>5.59</t>
-  </si>
-  <si>
-    <t>13.27</t>
-  </si>
-  <si>
-    <t>1.0973</t>
-  </si>
-  <si>
-    <t>967.6</t>
-  </si>
-  <si>
-    <t>4.17</t>
-  </si>
-  <si>
-    <t>13.29</t>
-  </si>
-  <si>
-    <t>1.0975</t>
+    <t>12.81</t>
+  </si>
+  <si>
+    <t>1.0943</t>
   </si>
   <si>
     <t>967.4</t>
   </si>
   <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>1.29</t>
-  </si>
-  <si>
-    <t>13.67</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>1.0977</t>
-  </si>
-  <si>
-    <t>13.66</t>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>12.52</t>
+  </si>
+  <si>
+    <t>1.0945</t>
+  </si>
+  <si>
+    <t>12.33</t>
+  </si>
+  <si>
+    <t>1.0944</t>
+  </si>
+  <si>
+    <t>12.13</t>
   </si>
   <si>
     <t>967.8</t>
-  </si>
-  <si>
-    <t>967.9</t>
-  </si>
-  <si>
-    <t>1.0968</t>
-  </si>
-  <si>
-    <t>13.65</t>
-  </si>
-  <si>
-    <t>1.0961</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>36.6</t>
-  </si>
-  <si>
-    <t>13.95</t>
-  </si>
-  <si>
-    <t>1.0955</t>
-  </si>
-  <si>
-    <t>13.64</t>
-  </si>
-  <si>
-    <t>1.0945</t>
-  </si>
-  <si>
-    <t>14.34</t>
-  </si>
-  <si>
-    <t>14.33</t>
-  </si>
-  <si>
-    <t>1.0922</t>
   </si>
 </sst>
 </file>
@@ -902,144 +896,132 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46084.979166666664</v>
+        <v>46089.979166666664</v>
       </c>
       <c r="B2" s="3">
-        <v>46077.0</v>
+        <v>46256.0</v>
       </c>
       <c r="C2" s="3">
-        <v>46105.0</v>
+        <v>46256.0</v>
       </c>
       <c r="D2" s="3">
-        <v>46077.0</v>
+        <v>46256.0</v>
       </c>
       <c r="E2" s="1">
         <v>92.0</v>
       </c>
       <c r="F2" s="3">
+        <v>46163.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L2" s="3">
         <v>46256.0</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>968.0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>94.0</v>
+      </c>
+      <c r="X2" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>46101.0</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>46232.0</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>46092.0</v>
+      </c>
+      <c r="AC2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="3">
-        <v>46077.0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>46079.0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>46079.0</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="U2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W2" s="4">
-        <v>123.0</v>
-      </c>
-      <c r="X2" s="3">
-        <v>46139.0</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>46134.0</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="AD2" s="1">
-        <v>696.0</v>
+        <v>693.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46084.958333333336</v>
+        <v>46089.958333333336</v>
       </c>
       <c r="B3" s="3">
-        <v>46105.0</v>
+        <v>46225.0</v>
       </c>
       <c r="C3" s="3">
-        <v>46136.0</v>
+        <v>46256.0</v>
       </c>
       <c r="D3" s="3">
-        <v>46077.0</v>
+        <v>46195.0</v>
       </c>
       <c r="E3" s="1">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="F3" s="3">
-        <v>46287.0</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
+        <v>46074.0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.0</v>
       </c>
       <c r="L3" s="3">
-        <v>46105.0</v>
+        <v>46225.0</v>
       </c>
       <c r="M3" s="3">
-        <v>46138.0</v>
+        <v>46046.0</v>
       </c>
       <c r="N3" s="3">
-        <v>46138.0</v>
+        <v>46046.0</v>
       </c>
       <c r="O3" s="1">
         <v>0.0</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>33</v>
+      <c r="P3" s="1">
+        <v>968.0</v>
       </c>
       <c r="Q3" s="1">
         <v>0.0</v>
@@ -1060,79 +1042,73 @@
         <v>0.0</v>
       </c>
       <c r="W3" s="4">
-        <v>125.0</v>
+        <v>91.0</v>
       </c>
       <c r="X3" s="3">
-        <v>46169.0</v>
+        <v>46050.0</v>
       </c>
       <c r="Y3" s="1">
-        <v>74.0</v>
+        <v>62.0</v>
       </c>
       <c r="Z3" s="3">
-        <v>46134.0</v>
+        <v>46042.0</v>
       </c>
       <c r="AA3" s="3">
-        <v>46052.0</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>37</v>
+        <v>46232.0</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>46033.0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>1093.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>695.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46084.9375</v>
+        <v>46089.9375</v>
       </c>
       <c r="B4" s="3">
-        <v>46166.0</v>
+        <v>46287.0</v>
       </c>
       <c r="C4" s="3">
-        <v>46166.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D4" s="3">
-        <v>46136.0</v>
+        <v>46256.0</v>
       </c>
       <c r="E4" s="1">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="F4" s="3">
+        <v>46074.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L4" s="3">
         <v>46287.0</v>
       </c>
-      <c r="G4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="M4" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="3">
-        <v>46166.0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>46199.0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>46199.0</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="Q4" s="1">
         <v>0.0</v>
       </c>
@@ -1152,170 +1128,158 @@
         <v>0.0</v>
       </c>
       <c r="W4" s="4">
-        <v>128.0</v>
+        <v>95.0</v>
       </c>
       <c r="X4" s="3">
-        <v>46200.0</v>
+        <v>46050.0</v>
       </c>
       <c r="Y4" s="1">
-        <v>73.0</v>
+        <v>62.0</v>
       </c>
       <c r="Z4" s="3">
-        <v>46103.0</v>
+        <v>46042.0</v>
       </c>
       <c r="AA4" s="3">
-        <v>46052.0</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>39</v>
+        <v>46232.0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>46033.0</v>
       </c>
       <c r="AC4" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AD4" s="1">
-        <v>694.0</v>
+        <v>691.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>46084.916666666664</v>
+        <v>46089.916666666664</v>
       </c>
       <c r="B5" s="3">
-        <v>46197.0</v>
+        <v>46076.0</v>
       </c>
       <c r="C5" s="3">
-        <v>46227.0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>46166.0</v>
+        <v>46135.0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>23.0</v>
       </c>
       <c r="E5" s="1">
-        <v>90.0</v>
+        <v>88.0</v>
       </c>
       <c r="F5" s="3">
-        <v>46287.0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="1" t="s">
+        <v>46043.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>46076.0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>46136.0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>46136.0</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W5" s="4">
+        <v>101.0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>46050.0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>46284.0</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="3">
-        <v>46197.0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>46229.0</v>
-      </c>
-      <c r="N5" s="3">
-        <v>46229.0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W5" s="4">
-        <v>131.0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>46200.0</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>46052.0</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="AD5" s="1">
-        <v>689.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>46084.895833333336</v>
+        <v>46089.895833333336</v>
       </c>
       <c r="B6" s="3">
-        <v>46227.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C6" s="3">
-        <v>46227.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D6" s="3">
-        <v>46227.0</v>
+        <v>46135.0</v>
       </c>
       <c r="E6" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>23.0</v>
+        <v>87.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46102.0</v>
       </c>
       <c r="G6" s="1">
         <v>0.0</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="I6" s="1">
         <v>0.0</v>
       </c>
-      <c r="J6" s="3">
-        <v>46082.0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>31</v>
+      <c r="J6" s="1">
+        <v>0.0</v>
       </c>
       <c r="L6" s="3">
-        <v>46227.0</v>
+        <v>46196.0</v>
       </c>
       <c r="M6" s="3">
-        <v>46260.0</v>
+        <v>46047.0</v>
       </c>
       <c r="N6" s="3">
-        <v>46260.0</v>
+        <v>46047.0</v>
       </c>
       <c r="O6" s="1">
         <v>0.0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="1">
         <v>0.0</v>
@@ -1335,79 +1299,73 @@
       <c r="V6" s="1">
         <v>0.0</v>
       </c>
-      <c r="W6" s="4">
-        <v>133.0</v>
+      <c r="W6" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="X6" s="3">
-        <v>46230.0</v>
+        <v>46081.0</v>
       </c>
       <c r="Y6" s="1">
-        <v>73.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z6" s="3">
-        <v>46134.0</v>
+        <v>46284.0</v>
       </c>
       <c r="AA6" s="3">
-        <v>46111.0</v>
+        <v>46232.0</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD6" s="1">
-        <v>698.0</v>
+        <v>686.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>46084.875</v>
+        <v>46089.875</v>
       </c>
       <c r="B7" s="3">
-        <v>46258.0</v>
+        <v>46257.0</v>
       </c>
       <c r="C7" s="3">
-        <v>46258.0</v>
+        <v>46046.0</v>
       </c>
       <c r="D7" s="3">
-        <v>46227.0</v>
+        <v>46165.0</v>
       </c>
       <c r="E7" s="1">
-        <v>89.0</v>
+        <v>85.0</v>
       </c>
       <c r="F7" s="3">
-        <v>46256.0</v>
+        <v>46074.0</v>
       </c>
       <c r="G7" s="1">
         <v>0.0</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="I7" s="1">
         <v>0.0</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>31</v>
+      <c r="J7" s="1">
+        <v>0.0</v>
       </c>
       <c r="L7" s="3">
-        <v>46258.0</v>
+        <v>46257.0</v>
       </c>
       <c r="M7" s="3">
-        <v>46260.0</v>
+        <v>46137.0</v>
       </c>
       <c r="N7" s="3">
-        <v>46260.0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0.0</v>
+        <v>46137.0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="1">
         <v>0.0</v>
@@ -1428,25 +1386,25 @@
         <v>0.0</v>
       </c>
       <c r="W7" s="4">
-        <v>134.0</v>
+        <v>115.0</v>
       </c>
       <c r="X7" s="3">
-        <v>46200.0</v>
+        <v>46109.0</v>
       </c>
       <c r="Y7" s="1">
-        <v>73.0</v>
+        <v>62.0</v>
       </c>
       <c r="Z7" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>39</v>
+        <v>46101.0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>46276.0</v>
       </c>
       <c r="AC7" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AD7" s="1">
         <v>696.0</v>
@@ -1454,52 +1412,46 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>46084.854166666664</v>
+        <v>46089.854166666664</v>
       </c>
       <c r="B8" s="3">
-        <v>46289.0</v>
+        <v>46257.0</v>
       </c>
       <c r="C8" s="1">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="D8" s="3">
-        <v>46258.0</v>
+        <v>46165.0</v>
       </c>
       <c r="E8" s="1">
-        <v>88.0</v>
+        <v>85.0</v>
       </c>
       <c r="F8" s="3">
-        <v>46256.0</v>
+        <v>46043.0</v>
       </c>
       <c r="G8" s="1">
         <v>0.0</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="I8" s="1">
         <v>0.0</v>
       </c>
-      <c r="J8" s="3">
-        <v>46082.0</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>31</v>
+      <c r="J8" s="1">
+        <v>0.0</v>
       </c>
       <c r="L8" s="3">
-        <v>46289.0</v>
+        <v>46257.0</v>
       </c>
       <c r="M8" s="3">
-        <v>46291.0</v>
+        <v>46106.0</v>
       </c>
       <c r="N8" s="3">
-        <v>46291.0</v>
+        <v>46106.0</v>
       </c>
       <c r="O8" s="1">
         <v>0.0</v>
       </c>
       <c r="P8" s="1">
-        <v>967.0</v>
+        <v>968.0</v>
       </c>
       <c r="Q8" s="1">
         <v>0.0</v>
@@ -1520,78 +1472,72 @@
         <v>0.0</v>
       </c>
       <c r="W8" s="4">
-        <v>137.0</v>
+        <v>113.0</v>
       </c>
       <c r="X8" s="3">
-        <v>46230.0</v>
+        <v>46109.0</v>
       </c>
       <c r="Y8" s="1">
-        <v>73.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z8" s="3">
-        <v>46134.0</v>
+        <v>46253.0</v>
       </c>
       <c r="AA8" s="3">
-        <v>46111.0</v>
+        <v>46263.0</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AC8" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AD8" s="1">
-        <v>693.0</v>
+        <v>692.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>46084.833333333336</v>
+        <v>46089.833333333336</v>
       </c>
       <c r="B9" s="3">
-        <v>46047.0</v>
+        <v>46046.0</v>
       </c>
       <c r="C9" s="3">
-        <v>46078.0</v>
+        <v>46046.0</v>
       </c>
       <c r="D9" s="1">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="E9" s="1">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="F9" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>31</v>
+        <v>46286.0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.0</v>
       </c>
       <c r="L9" s="3">
-        <v>46047.0</v>
+        <v>46046.0</v>
       </c>
       <c r="M9" s="3">
-        <v>46108.0</v>
+        <v>46290.0</v>
       </c>
       <c r="N9" s="3">
-        <v>46108.0</v>
+        <v>46290.0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q9" s="1">
         <v>0.0</v>
@@ -1612,78 +1558,72 @@
         <v>0.0</v>
       </c>
       <c r="W9" s="4">
-        <v>141.0</v>
+        <v>119.0</v>
       </c>
       <c r="X9" s="3">
-        <v>46230.0</v>
+        <v>46140.0</v>
       </c>
       <c r="Y9" s="1">
-        <v>73.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z9" s="3">
-        <v>46134.0</v>
+        <v>46042.0</v>
       </c>
       <c r="AA9" s="3">
-        <v>46111.0</v>
+        <v>46052.0</v>
       </c>
       <c r="AB9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AC9" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="AD9" s="1">
-        <v>693.0</v>
+        <v>691.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>46084.8125</v>
+        <v>46089.8125</v>
       </c>
       <c r="B10" s="3">
-        <v>46106.0</v>
+        <v>46077.0</v>
       </c>
       <c r="C10" s="3">
-        <v>46137.0</v>
+        <v>46136.0</v>
       </c>
       <c r="D10" s="3">
-        <v>46078.0</v>
+        <v>46046.0</v>
       </c>
       <c r="E10" s="1">
         <v>86.0</v>
       </c>
       <c r="F10" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>31</v>
+        <v>46224.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.0</v>
       </c>
       <c r="L10" s="3">
-        <v>46106.0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>46169.0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>46169.0</v>
+        <v>46077.0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>26.0</v>
       </c>
       <c r="O10" s="1">
         <v>0.0</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>52</v>
+      <c r="P10" s="1">
+        <v>967.0</v>
       </c>
       <c r="Q10" s="1">
         <v>0.0</v>
@@ -1704,78 +1644,72 @@
         <v>0.0</v>
       </c>
       <c r="W10" s="4">
-        <v>145.0</v>
+        <v>123.0</v>
       </c>
       <c r="X10" s="3">
-        <v>46230.0</v>
+        <v>46140.0</v>
       </c>
       <c r="Y10" s="1">
-        <v>72.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z10" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>46111.0</v>
+        <v>46073.0</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AC10" s="5" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AD10" s="1">
-        <v>692.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>46084.791666666664</v>
+        <v>46089.791666666664</v>
       </c>
       <c r="B11" s="3">
-        <v>46167.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C11" s="3">
-        <v>46228.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D11" s="3">
-        <v>46137.0</v>
+        <v>46105.0</v>
       </c>
       <c r="E11" s="1">
-        <v>85.0</v>
+        <v>83.0</v>
       </c>
       <c r="F11" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>31</v>
+        <v>46163.0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.0</v>
       </c>
       <c r="L11" s="3">
-        <v>46167.0</v>
+        <v>46197.0</v>
       </c>
       <c r="M11" s="3">
-        <v>46230.0</v>
+        <v>46138.0</v>
       </c>
       <c r="N11" s="3">
-        <v>46230.0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0.0</v>
+        <v>46138.0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Q11" s="1">
         <v>0.0</v>
@@ -1796,78 +1730,72 @@
         <v>0.0</v>
       </c>
       <c r="W11" s="4">
-        <v>149.0</v>
+        <v>131.0</v>
       </c>
       <c r="X11" s="3">
-        <v>46261.0</v>
+        <v>46140.0</v>
       </c>
       <c r="Y11" s="1">
-        <v>72.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z11" s="3">
-        <v>46103.0</v>
+        <v>46284.0</v>
       </c>
       <c r="AA11" s="3">
-        <v>46142.0</v>
+        <v>46052.0</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC11" s="4">
-        <v>1087.0</v>
+        <v>41</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="AD11" s="1">
-        <v>690.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>46084.770833333336</v>
-      </c>
-      <c r="B12" s="1">
-        <v>26.0</v>
+        <v>46089.770833333336</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46137.0</v>
       </c>
       <c r="C12" s="3">
-        <v>46079.0</v>
+        <v>46259.0</v>
       </c>
       <c r="D12" s="3">
-        <v>46228.0</v>
+        <v>46289.0</v>
       </c>
       <c r="E12" s="1">
-        <v>84.0</v>
+        <v>83.0</v>
       </c>
       <c r="F12" s="3">
-        <v>46045.0</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" s="3">
-        <v>46055.0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="1">
-        <v>26.0</v>
+        <v>46103.0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>46137.0</v>
       </c>
       <c r="M12" s="3">
-        <v>46140.0</v>
+        <v>46139.0</v>
       </c>
       <c r="N12" s="3">
-        <v>46140.0</v>
+        <v>46139.0</v>
       </c>
       <c r="O12" s="1">
         <v>0.0</v>
       </c>
-      <c r="P12" s="1">
-        <v>965.0</v>
+      <c r="P12" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="Q12" s="1">
         <v>0.0</v>
@@ -1887,79 +1815,73 @@
       <c r="V12" s="1">
         <v>0.0</v>
       </c>
-      <c r="W12" s="1" t="s">
-        <v>57</v>
+      <c r="W12" s="4">
+        <v>147.0</v>
       </c>
       <c r="X12" s="3">
-        <v>46292.0</v>
+        <v>46170.0</v>
       </c>
       <c r="Y12" s="1">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z12" s="3">
-        <v>46044.0</v>
+        <v>46073.0</v>
       </c>
       <c r="AA12" s="3">
-        <v>46203.0</v>
+        <v>46111.0</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AC12" s="5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD12" s="1">
-        <v>695.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>46084.75</v>
+        <v>46089.75</v>
       </c>
       <c r="B13" s="3">
-        <v>46138.0</v>
+        <v>46107.0</v>
       </c>
       <c r="C13" s="3">
         <v>46229.0</v>
       </c>
       <c r="D13" s="3">
+        <v>46259.0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="3">
         <v>46107.0</v>
       </c>
-      <c r="E13" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>46104.0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="3">
-        <v>46055.0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="3">
-        <v>46138.0</v>
-      </c>
       <c r="M13" s="3">
-        <v>46051.0</v>
+        <v>46170.0</v>
       </c>
       <c r="N13" s="3">
-        <v>46051.0</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>60</v>
+        <v>46170.0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0.0</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="1">
         <v>0.0</v>
@@ -1968,90 +1890,84 @@
         <v>0.0</v>
       </c>
       <c r="S13" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>62</v>
+        <v>0.0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.0</v>
       </c>
       <c r="U13" s="1">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
       <c r="V13" s="1">
         <v>0.0</v>
       </c>
       <c r="W13" s="4">
-        <v>169.0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>28.0</v>
+        <v>166.0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>46201.0</v>
       </c>
       <c r="Y13" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>22.0</v>
+        <v>61.0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>46101.0</v>
       </c>
       <c r="AA13" s="3">
-        <v>46203.0</v>
+        <v>46142.0</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC13" s="5" t="s">
-        <v>64</v>
+        <v>35</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>1089.0</v>
       </c>
       <c r="AD13" s="1">
-        <v>694.0</v>
+        <v>699.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>46084.729166666664</v>
+        <v>46089.729166666664</v>
       </c>
       <c r="B14" s="3">
+        <v>46169.0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46140.0</v>
+      </c>
+      <c r="D14" s="3">
         <v>46260.0</v>
       </c>
-      <c r="C14" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D14" s="3">
-        <v>46229.0</v>
-      </c>
       <c r="E14" s="1">
-        <v>82.0</v>
+        <v>75.0</v>
       </c>
       <c r="F14" s="3">
-        <v>46165.0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>46082.0</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>31</v>
+        <v>46225.0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.0</v>
       </c>
       <c r="L14" s="3">
-        <v>46260.0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>46263.0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>46263.0</v>
+        <v>46169.0</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="O14" s="1">
         <v>0.0</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="1">
         <v>0.0</v>
@@ -2060,90 +1976,90 @@
         <v>0.0</v>
       </c>
       <c r="S14" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>67</v>
+        <v>0.0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.0</v>
       </c>
       <c r="U14" s="1">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
       <c r="V14" s="1">
         <v>0.0</v>
       </c>
       <c r="W14" s="4">
-        <v>177.0</v>
+        <v>191.0</v>
       </c>
       <c r="X14" s="3">
-        <v>46050.0</v>
+        <v>46231.0</v>
       </c>
       <c r="Y14" s="1">
-        <v>68.0</v>
+        <v>62.0</v>
       </c>
       <c r="Z14" s="3">
-        <v>46194.0</v>
+        <v>46223.0</v>
       </c>
       <c r="AA14" s="3">
-        <v>46203.0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>46093.0</v>
+        <v>46264.0</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>46245.0</v>
       </c>
       <c r="AC14" s="5" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="AD14" s="1">
-        <v>687.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>46084.708333333336</v>
+        <v>46089.708333333336</v>
       </c>
       <c r="B15" s="3">
-        <v>46108.0</v>
+        <v>46051.0</v>
       </c>
       <c r="C15" s="3">
-        <v>46292.0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>27.0</v>
+        <v>46232.0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46140.0</v>
       </c>
       <c r="E15" s="1">
-        <v>79.0</v>
+        <v>65.0</v>
       </c>
       <c r="F15" s="3">
-        <v>46135.0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>46235.0</v>
+        <v>46255.0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="J15" s="3">
-        <v>46176.0</v>
+        <v>46082.0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L15" s="3">
-        <v>46108.0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>46142.0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>46142.0</v>
+        <v>46051.0</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="P15" s="1">
-        <v>965.0</v>
+        <v>56</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="Q15" s="1">
         <v>0.0</v>
@@ -2152,90 +2068,90 @@
         <v>0.0</v>
       </c>
       <c r="S15" s="1">
-        <v>113.0</v>
+        <v>16.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="U15" s="1">
-        <v>127.0</v>
+        <v>42.0</v>
       </c>
       <c r="V15" s="1">
         <v>0.0</v>
       </c>
       <c r="W15" s="4">
-        <v>187.0</v>
+        <v>223.0</v>
       </c>
       <c r="X15" s="3">
-        <v>46140.0</v>
+        <v>46293.0</v>
       </c>
       <c r="Y15" s="1">
-        <v>65.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z15" s="3">
-        <v>46074.0</v>
+        <v>46193.0</v>
       </c>
       <c r="AA15" s="3">
-        <v>46203.0</v>
+        <v>46053.0</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="AC15" s="5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="AD15" s="1">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>46084.6875</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46231.0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>46051.0</v>
+        <v>46089.6875</v>
+      </c>
+      <c r="B16" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="D16" s="3">
-        <v>46292.0</v>
+        <v>46232.0</v>
       </c>
       <c r="E16" s="1">
-        <v>78.0</v>
+        <v>56.0</v>
       </c>
       <c r="F16" s="3">
-        <v>46136.0</v>
-      </c>
-      <c r="G16" s="3">
-        <v>46082.0</v>
+        <v>46101.0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" s="1">
-        <v>4.0</v>
+        <v>61</v>
+      </c>
+      <c r="J16" s="3">
+        <v>46235.0</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="3">
-        <v>46231.0</v>
+        <v>53</v>
+      </c>
+      <c r="L16" s="1">
+        <v>30.0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O16" s="1">
         <v>0.0</v>
       </c>
       <c r="P16" s="1">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
       <c r="Q16" s="1">
         <v>0.0</v>
@@ -2244,182 +2160,182 @@
         <v>0.0</v>
       </c>
       <c r="S16" s="1">
-        <v>349.0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>46037.0</v>
+        <v>100.0</v>
+      </c>
+      <c r="T16" s="3">
+        <v>46085.0</v>
       </c>
       <c r="U16" s="1">
-        <v>664.0</v>
+        <v>163.0</v>
       </c>
       <c r="V16" s="1">
         <v>0.0</v>
       </c>
       <c r="W16" s="4">
-        <v>215.0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>46231.0</v>
+        <v>243.0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>29.0</v>
       </c>
       <c r="Y16" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>22.0</v>
+        <v>61.0</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>46223.0</v>
       </c>
       <c r="AA16" s="3">
-        <v>46265.0</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>46246.0</v>
+        <v>46112.0</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="AC16" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AD16" s="1">
-        <v>691.0</v>
+        <v>692.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>46084.666666666664</v>
+        <v>46089.666666666664</v>
       </c>
       <c r="B17" s="3">
-        <v>46231.0</v>
+        <v>46111.0</v>
       </c>
       <c r="C17" s="3">
-        <v>46262.0</v>
-      </c>
-      <c r="D17" s="3">
-        <v>46170.0</v>
+        <v>46142.0</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E17" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>24.0</v>
+        <v>52.0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46131.0</v>
       </c>
       <c r="G17" s="3">
-        <v>46235.0</v>
+        <v>46082.0</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="3">
+        <v>46111.0</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P17" s="1">
+        <v>966.0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>237.0</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="U17" s="1">
+        <v>301.0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="X17" s="3">
+        <v>46051.0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>46162.0</v>
+      </c>
+      <c r="AA17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="3">
-        <v>46231.0</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>550.0</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="U17" s="1">
-        <v>694.0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W17" s="4">
-        <v>215.0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>46231.0</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>46265.0</v>
-      </c>
-      <c r="AB17" s="6">
-        <v>46246.0</v>
+      <c r="AB17" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AC17" s="5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="AD17" s="1">
-        <v>692.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>46084.645833333336</v>
+        <v>46089.645833333336</v>
       </c>
       <c r="B18" s="3">
-        <v>46231.0</v>
+        <v>46203.0</v>
       </c>
       <c r="C18" s="3">
-        <v>46231.0</v>
+        <v>46264.0</v>
       </c>
       <c r="D18" s="3">
-        <v>46170.0</v>
+        <v>46111.0</v>
       </c>
       <c r="E18" s="1">
-        <v>75.0</v>
+        <v>53.0</v>
       </c>
       <c r="F18" s="3">
-        <v>46257.0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>46082.0</v>
+        <v>46284.0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J18" s="3">
-        <v>46025.0</v>
+        <v>46176.0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="L18" s="3">
-        <v>46231.0</v>
+        <v>46203.0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="O18" s="1">
         <v>0.0</v>
       </c>
       <c r="P18" s="1">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
       <c r="Q18" s="1">
         <v>0.0</v>
@@ -2428,90 +2344,90 @@
         <v>0.0</v>
       </c>
       <c r="S18" s="1">
-        <v>465.0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>20.0</v>
+        <v>357.0</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="U18" s="1">
-        <v>738.0</v>
+        <v>445.0</v>
       </c>
       <c r="V18" s="1">
         <v>0.0</v>
       </c>
       <c r="W18" s="4">
-        <v>215.0</v>
+        <v>255.0</v>
       </c>
       <c r="X18" s="3">
-        <v>46293.0</v>
+        <v>46051.0</v>
       </c>
       <c r="Y18" s="1">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z18" s="3">
-        <v>46287.0</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>46185.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>46112.0</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AC18" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="AD18" s="1">
-        <v>695.0</v>
+        <v>697.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>46084.625</v>
+        <v>46089.625</v>
       </c>
       <c r="B19" s="3">
-        <v>46109.0</v>
+        <v>46264.0</v>
       </c>
       <c r="C19" s="3">
-        <v>46201.0</v>
+        <v>46295.0</v>
       </c>
       <c r="D19" s="3">
-        <v>46050.0</v>
+        <v>46172.0</v>
       </c>
       <c r="E19" s="1">
-        <v>76.0</v>
+        <v>53.0</v>
       </c>
       <c r="F19" s="3">
-        <v>46196.0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>46235.0</v>
+        <v>46042.0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J19" s="3">
-        <v>46176.0</v>
+        <v>46025.0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L19" s="3">
-        <v>46109.0</v>
+        <v>46264.0</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="1">
         <v>0.0</v>
@@ -2520,90 +2436,90 @@
         <v>0.0</v>
       </c>
       <c r="S19" s="1">
-        <v>483.0</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>89</v>
+        <v>493.0</v>
+      </c>
+      <c r="T19" s="3">
+        <v>46074.0</v>
       </c>
       <c r="U19" s="1">
-        <v>696.0</v>
+        <v>573.0</v>
       </c>
       <c r="V19" s="1">
         <v>0.0</v>
       </c>
       <c r="W19" s="4">
-        <v>207.0</v>
-      </c>
-      <c r="X19" s="1">
-        <v>29.0</v>
+        <v>259.0</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="Y19" s="1">
-        <v>69.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z19" s="3">
-        <v>46225.0</v>
+        <v>46193.0</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC19" s="4">
-        <v>1082.0</v>
+        <v>41</v>
+      </c>
+      <c r="AC19" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="AD19" s="1">
-        <v>696.0</v>
+        <v>692.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>46084.604166666664</v>
+        <v>46089.604166666664</v>
       </c>
       <c r="B20" s="3">
-        <v>46170.0</v>
+        <v>46264.0</v>
       </c>
       <c r="C20" s="3">
-        <v>46262.0</v>
+        <v>46053.0</v>
       </c>
       <c r="D20" s="3">
-        <v>46050.0</v>
+        <v>46142.0</v>
       </c>
       <c r="E20" s="1">
-        <v>75.0</v>
+        <v>53.0</v>
       </c>
       <c r="F20" s="3">
-        <v>46196.0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>46082.0</v>
+        <v>46042.0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J20" s="1">
-        <v>4.0</v>
+        <v>61</v>
+      </c>
+      <c r="J20" s="3">
+        <v>46176.0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L20" s="3">
-        <v>46170.0</v>
+        <v>46264.0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="O20" s="1">
         <v>0.0</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="1">
         <v>0.0</v>
@@ -2612,84 +2528,90 @@
         <v>0.0</v>
       </c>
       <c r="S20" s="1">
-        <v>763.0</v>
+        <v>527.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="U20" s="1">
-        <v>995.0</v>
+        <v>687.0</v>
       </c>
       <c r="V20" s="1">
         <v>0.0</v>
       </c>
       <c r="W20" s="4">
-        <v>212.0</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>94</v>
+        <v>259.0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>46110.0</v>
       </c>
       <c r="Y20" s="1">
-        <v>69.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z20" s="3">
-        <v>46287.0</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>83</v>
+        <v>46254.0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>46234.0</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="AC20" s="5" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AD20" s="1">
-        <v>692.0</v>
+        <v>696.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>46084.583333333336</v>
+        <v>46089.583333333336</v>
       </c>
       <c r="B21" s="3">
-        <v>46050.0</v>
+        <v>46264.0</v>
       </c>
       <c r="C21" s="3">
-        <v>46170.0</v>
+        <v>46295.0</v>
       </c>
       <c r="D21" s="3">
-        <v>46139.0</v>
+        <v>46142.0</v>
       </c>
       <c r="E21" s="1">
-        <v>77.0</v>
+        <v>52.0</v>
       </c>
       <c r="F21" s="3">
-        <v>46196.0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0.0</v>
+        <v>46253.0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J21" s="1">
-        <v>0.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="L21" s="3">
-        <v>46050.0</v>
+        <v>46264.0</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q21" s="1">
         <v>0.0</v>
@@ -2698,90 +2620,90 @@
         <v>0.0</v>
       </c>
       <c r="S21" s="1">
-        <v>791.0</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>99</v>
+        <v>744.0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>32.0</v>
       </c>
       <c r="U21" s="1">
-        <v>1201.0</v>
+        <v>861.0</v>
       </c>
       <c r="V21" s="1">
         <v>0.0</v>
       </c>
       <c r="W21" s="4">
-        <v>203.0</v>
+        <v>259.0</v>
       </c>
       <c r="X21" s="3">
         <v>46110.0</v>
       </c>
       <c r="Y21" s="1">
-        <v>68.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z21" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>83</v>
+        <v>46254.0</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>46234.0</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="AC21" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="AD21" s="1">
-        <v>691.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>46084.5625</v>
+        <v>46089.5625</v>
       </c>
       <c r="B22" s="3">
-        <v>46200.0</v>
+        <v>46203.0</v>
       </c>
       <c r="C22" s="3">
-        <v>46230.0</v>
-      </c>
-      <c r="D22" s="3">
-        <v>46139.0</v>
+        <v>46295.0</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E22" s="1">
-        <v>79.0</v>
+        <v>55.0</v>
       </c>
       <c r="F22" s="3">
-        <v>46196.0</v>
+        <v>46162.0</v>
       </c>
       <c r="G22" s="3">
-        <v>46082.0</v>
+        <v>46235.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="J22" s="3">
         <v>46146.0</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L22" s="3">
-        <v>46200.0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>46295.0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>46295.0</v>
+        <v>46203.0</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="O22" s="1">
         <v>0.0</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="1">
         <v>0.0</v>
@@ -2790,90 +2712,90 @@
         <v>0.0</v>
       </c>
       <c r="S22" s="1">
-        <v>605.0</v>
-      </c>
-      <c r="T22" s="6">
-        <v>46079.0</v>
+        <v>829.0</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="U22" s="1">
-        <v>868.0</v>
+        <v>909.0</v>
       </c>
       <c r="V22" s="1">
         <v>0.0</v>
       </c>
       <c r="W22" s="4">
-        <v>192.0</v>
+        <v>255.0</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="Y22" s="1">
-        <v>68.0</v>
+        <v>59.0</v>
       </c>
       <c r="Z22" s="3">
-        <v>46225.0</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>33.0</v>
+        <v>46132.0</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="AC22" s="5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="AD22" s="1">
-        <v>696.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>46084.541666666664</v>
-      </c>
-      <c r="B23" s="3">
-        <v>46139.0</v>
+        <v>46089.541666666664</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C23" s="3">
-        <v>46200.0</v>
+        <v>46111.0</v>
       </c>
       <c r="D23" s="3">
-        <v>46049.0</v>
+        <v>46263.0</v>
       </c>
       <c r="E23" s="1">
-        <v>79.0</v>
+        <v>55.0</v>
       </c>
       <c r="F23" s="3">
-        <v>46135.0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>36</v>
+        <v>46042.0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>46235.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="J23" s="3">
         <v>46146.0</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L23" s="3">
-        <v>46139.0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>46203.0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>46203.0</v>
+        <v>64</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="1">
         <v>0.0</v>
@@ -2882,84 +2804,90 @@
         <v>0.0</v>
       </c>
       <c r="S23" s="1">
-        <v>696.0</v>
+        <v>811.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="U23" s="1">
-        <v>1157.0</v>
+        <v>1027.0</v>
       </c>
       <c r="V23" s="1">
         <v>0.0</v>
       </c>
       <c r="W23" s="4">
-        <v>189.0</v>
-      </c>
-      <c r="X23" s="1">
-        <v>29.0</v>
+        <v>247.0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>46051.0</v>
       </c>
       <c r="Y23" s="1">
-        <v>68.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z23" s="3">
-        <v>46164.0</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>107</v>
+        <v>46193.0</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>46112.0</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="AC23" s="5" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="AD23" s="1">
-        <v>694.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>46084.520833333336</v>
+        <v>46089.520833333336</v>
       </c>
       <c r="B24" s="3">
-        <v>46291.0</v>
+        <v>46263.0</v>
       </c>
       <c r="C24" s="3">
-        <v>46049.0</v>
+        <v>46052.0</v>
       </c>
       <c r="D24" s="3">
-        <v>46260.0</v>
+        <v>46202.0</v>
       </c>
       <c r="E24" s="1">
-        <v>81.0</v>
+        <v>57.0</v>
       </c>
       <c r="F24" s="3">
-        <v>46135.0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0.0</v>
+        <v>46132.0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="3">
+        <v>46117.0</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="L24" s="3">
-        <v>46291.0</v>
-      </c>
-      <c r="M24" s="3">
         <v>46263.0</v>
       </c>
-      <c r="N24" s="3">
-        <v>46263.0</v>
+      <c r="M24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="O24" s="1">
         <v>0.0</v>
       </c>
-      <c r="P24" s="1">
-        <v>968.0</v>
+      <c r="P24" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="Q24" s="1">
         <v>0.0</v>
@@ -2968,84 +2896,90 @@
         <v>0.0</v>
       </c>
       <c r="S24" s="1">
-        <v>591.0</v>
+        <v>816.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="U24" s="1">
-        <v>657.0</v>
+        <v>1097.0</v>
       </c>
       <c r="V24" s="1">
         <v>0.0</v>
       </c>
-      <c r="W24" s="4">
-        <v>179.0</v>
+      <c r="W24" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="X24" s="3">
-        <v>46262.0</v>
+        <v>46051.0</v>
       </c>
       <c r="Y24" s="1">
-        <v>68.0</v>
+        <v>60.0</v>
       </c>
       <c r="Z24" s="3">
-        <v>46103.0</v>
+        <v>46162.0</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="AC24" s="5" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="AD24" s="1">
-        <v>697.0</v>
+        <v>696.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>46084.5</v>
+        <v>46089.5</v>
       </c>
       <c r="B25" s="3">
-        <v>46138.0</v>
+        <v>46202.0</v>
       </c>
       <c r="C25" s="3">
-        <v>46260.0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>26.0</v>
+        <v>46294.0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>46110.0</v>
       </c>
       <c r="E25" s="1">
-        <v>81.0</v>
+        <v>57.0</v>
       </c>
       <c r="F25" s="3">
-        <v>46287.0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0.0</v>
+        <v>46073.0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="3">
+        <v>46117.0</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="L25" s="3">
-        <v>46138.0</v>
+        <v>46202.0</v>
       </c>
       <c r="M25" s="3">
-        <v>46293.0</v>
+        <v>46234.0</v>
       </c>
       <c r="N25" s="3">
-        <v>46293.0</v>
+        <v>46234.0</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="Q25" s="1">
         <v>0.0</v>
@@ -3054,84 +2988,90 @@
         <v>0.0</v>
       </c>
       <c r="S25" s="1">
-        <v>584.0</v>
-      </c>
-      <c r="T25" s="3">
-        <v>46381.0</v>
+        <v>955.0</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="U25" s="1">
-        <v>643.0</v>
+        <v>1171.0</v>
       </c>
       <c r="V25" s="1">
         <v>0.0</v>
       </c>
       <c r="W25" s="4">
-        <v>169.0</v>
-      </c>
-      <c r="X25" s="3">
-        <v>46231.0</v>
+        <v>235.0</v>
+      </c>
+      <c r="X25" s="1">
+        <v>29.0</v>
       </c>
       <c r="Y25" s="1">
-        <v>68.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z25" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="AA25" s="1" t="s">
-        <v>97</v>
+        <v>46223.0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>46112.0</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="AC25" s="5" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="AD25" s="1">
-        <v>696.0</v>
+        <v>692.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>46084.479166666664</v>
+        <v>46089.479166666664</v>
       </c>
       <c r="B26" s="3">
-        <v>46228.0</v>
-      </c>
-      <c r="C26" s="1">
-        <v>26.0</v>
+        <v>46051.0</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46202.0</v>
       </c>
       <c r="D26" s="3">
-        <v>46137.0</v>
+        <v>46262.0</v>
       </c>
       <c r="E26" s="1">
-        <v>81.0</v>
+        <v>60.0</v>
       </c>
       <c r="F26" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>46055.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="6">
+        <v>46057.0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>46117.0</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="L26" s="3">
-        <v>46228.0</v>
+        <v>46051.0</v>
       </c>
       <c r="M26" s="3">
-        <v>46230.0</v>
+        <v>46112.0</v>
       </c>
       <c r="N26" s="3">
-        <v>46230.0</v>
+        <v>46112.0</v>
       </c>
       <c r="O26" s="1">
         <v>0.0</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="1">
         <v>0.0</v>
@@ -3140,37 +3080,37 @@
         <v>0.0</v>
       </c>
       <c r="S26" s="1">
-        <v>528.0</v>
+        <v>1047.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="U26" s="1">
-        <v>543.0</v>
+        <v>1202.0</v>
       </c>
       <c r="V26" s="1">
         <v>0.0</v>
       </c>
       <c r="W26" s="4">
-        <v>153.0</v>
+        <v>225.0</v>
       </c>
       <c r="X26" s="3">
-        <v>46201.0</v>
+        <v>46293.0</v>
       </c>
       <c r="Y26" s="1">
-        <v>68.0</v>
+        <v>61.0</v>
       </c>
       <c r="Z26" s="3">
-        <v>46044.0</v>
-      </c>
-      <c r="AA26" s="1" t="s">
-        <v>117</v>
+        <v>46193.0</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>46053.0</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC26" s="4">
-        <v>1089.0</v>
+        <v>35</v>
+      </c>
+      <c r="AC26" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="AD26" s="1">
         <v>691.0</v>
@@ -3178,46 +3118,52 @@
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>46084.458333333336</v>
-      </c>
-      <c r="B27" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="C27" s="3">
-        <v>46137.0</v>
+        <v>46089.458333333336</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46262.0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>29.0</v>
       </c>
       <c r="D27" s="3">
-        <v>46166.0</v>
+        <v>46201.0</v>
       </c>
       <c r="E27" s="1">
-        <v>83.0</v>
+        <v>61.0</v>
       </c>
       <c r="F27" s="3">
-        <v>46286.0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>46291.0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>46291.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>46055.0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="6">
+        <v>46057.0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>46269.0</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="3">
+        <v>46262.0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>31.0</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="1">
         <v>0.0</v>
@@ -3226,84 +3172,90 @@
         <v>0.0</v>
       </c>
       <c r="S27" s="1">
-        <v>539.0</v>
+        <v>1056.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="U27" s="1">
-        <v>631.0</v>
+        <v>1148.0</v>
       </c>
       <c r="V27" s="1">
         <v>0.0</v>
       </c>
       <c r="W27" s="4">
-        <v>139.0</v>
+        <v>219.0</v>
       </c>
       <c r="X27" s="3">
-        <v>46140.0</v>
+        <v>46231.0</v>
       </c>
       <c r="Y27" s="1">
-        <v>68.0</v>
+        <v>62.0</v>
       </c>
       <c r="Z27" s="3">
-        <v>46286.0</v>
+        <v>46223.0</v>
       </c>
       <c r="AA27" s="3">
-        <v>46053.0</v>
-      </c>
-      <c r="AB27" s="1" t="s">
-        <v>121</v>
+        <v>46295.0</v>
+      </c>
+      <c r="AB27" s="6">
+        <v>46245.0</v>
       </c>
       <c r="AC27" s="5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AD27" s="1">
-        <v>694.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>46084.4375</v>
+        <v>46089.4375</v>
       </c>
       <c r="B28" s="3">
-        <v>46288.0</v>
+        <v>46081.0</v>
       </c>
       <c r="C28" s="3">
-        <v>46166.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D28" s="3">
-        <v>46165.0</v>
+        <v>46261.0</v>
       </c>
       <c r="E28" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>0.0</v>
+        <v>65.0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="3">
+        <v>46269.0</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="L28" s="3">
-        <v>46288.0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>46259.0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>46259.0</v>
+        <v>46081.0</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="O28" s="1">
         <v>0.0</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="1">
         <v>0.0</v>
@@ -3312,84 +3264,90 @@
         <v>0.0</v>
       </c>
       <c r="S28" s="1">
-        <v>506.0</v>
+        <v>1083.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="U28" s="1">
-        <v>599.0</v>
+        <v>1271.0</v>
       </c>
       <c r="V28" s="1">
         <v>0.0</v>
       </c>
       <c r="W28" s="4">
-        <v>116.0</v>
+        <v>205.0</v>
       </c>
       <c r="X28" s="3">
-        <v>46081.0</v>
+        <v>46231.0</v>
       </c>
       <c r="Y28" s="1">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
       <c r="Z28" s="3">
-        <v>46286.0</v>
+        <v>46285.0</v>
       </c>
       <c r="AA28" s="3">
-        <v>46264.0</v>
+        <v>46295.0</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="AC28" s="5" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="AD28" s="1">
-        <v>693.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>46084.416666666664</v>
+        <v>46089.416666666664</v>
       </c>
       <c r="B29" s="3">
-        <v>46045.0</v>
+        <v>46139.0</v>
       </c>
       <c r="C29" s="3">
-        <v>46196.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D29" s="3">
-        <v>46195.0</v>
+        <v>46080.0</v>
       </c>
       <c r="E29" s="1">
-        <v>96.0</v>
+        <v>65.0</v>
       </c>
       <c r="F29" s="3">
-        <v>46134.0</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>0.0</v>
+        <v>46073.0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>46055.0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="6">
+        <v>46057.0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>46146.0</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="L29" s="3">
-        <v>46045.0</v>
+        <v>46139.0</v>
       </c>
       <c r="M29" s="3">
-        <v>46227.0</v>
+        <v>46293.0</v>
       </c>
       <c r="N29" s="3">
-        <v>46227.0</v>
+        <v>46293.0</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="1">
         <v>0.0</v>
@@ -3398,90 +3356,90 @@
         <v>0.0</v>
       </c>
       <c r="S29" s="1">
-        <v>657.0</v>
+        <v>654.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="U29" s="1">
-        <v>928.0</v>
+        <v>1218.0</v>
       </c>
       <c r="V29" s="1">
         <v>0.0</v>
       </c>
       <c r="W29" s="4">
-        <v>98.0</v>
+        <v>189.0</v>
       </c>
       <c r="X29" s="3">
-        <v>46292.0</v>
+        <v>46201.0</v>
       </c>
       <c r="Y29" s="1">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
       <c r="Z29" s="3">
-        <v>46224.0</v>
+        <v>46254.0</v>
       </c>
       <c r="AA29" s="3">
-        <v>46111.0</v>
+        <v>46233.0</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="AC29" s="5" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="AD29" s="1">
-        <v>693.0</v>
+        <v>692.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>46084.395833333336</v>
-      </c>
-      <c r="B30" s="3">
-        <v>46134.0</v>
+        <v>46089.395833333336</v>
+      </c>
+      <c r="B30" s="1">
+        <v>27.0</v>
       </c>
       <c r="C30" s="3">
-        <v>46256.0</v>
+        <v>46230.0</v>
       </c>
       <c r="D30" s="3">
-        <v>46044.0</v>
+        <v>46168.0</v>
       </c>
       <c r="E30" s="1">
-        <v>97.0</v>
+        <v>68.0</v>
       </c>
       <c r="F30" s="3">
-        <v>46286.0</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G30" s="3">
+        <v>46055.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>36</v>
+        <v>95</v>
+      </c>
+      <c r="I30" s="6">
+        <v>46057.0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>46117.0</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L30" s="3">
-        <v>46134.0</v>
+        <v>64</v>
+      </c>
+      <c r="L30" s="1">
+        <v>27.0</v>
       </c>
       <c r="M30" s="3">
-        <v>46077.0</v>
+        <v>46201.0</v>
       </c>
       <c r="N30" s="3">
-        <v>46077.0</v>
+        <v>46201.0</v>
       </c>
       <c r="O30" s="1">
         <v>0.0</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="1">
         <v>0.0</v>
@@ -3490,182 +3448,182 @@
         <v>0.0</v>
       </c>
       <c r="S30" s="1">
-        <v>511.0</v>
+        <v>831.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="U30" s="1">
-        <v>714.0</v>
+        <v>1185.0</v>
       </c>
       <c r="V30" s="1">
         <v>0.0</v>
       </c>
       <c r="W30" s="4">
-        <v>86.0</v>
+        <v>181.0</v>
       </c>
       <c r="X30" s="3">
-        <v>46108.0</v>
+        <v>46201.0</v>
       </c>
       <c r="Y30" s="1">
-        <v>70.0</v>
+        <v>63.0</v>
       </c>
       <c r="Z30" s="3">
-        <v>46133.0</v>
+        <v>46254.0</v>
       </c>
       <c r="AA30" s="3">
-        <v>46110.0</v>
+        <v>46233.0</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="AC30" s="5" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="AD30" s="1">
-        <v>696.0</v>
+        <v>697.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>46084.375</v>
-      </c>
-      <c r="B31" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C31" s="3">
-        <v>46075.0</v>
+        <v>46089.375</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46260.0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>27.0</v>
       </c>
       <c r="D31" s="3">
-        <v>46286.0</v>
+        <v>46199.0</v>
       </c>
       <c r="E31" s="1">
-        <v>96.0</v>
+        <v>69.0</v>
       </c>
       <c r="F31" s="3">
-        <v>46102.0</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>30</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>46205.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="J31" s="3">
-        <v>46082.0</v>
+        <v>46239.0</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L31" s="1">
-        <v>22.0</v>
+        <v>53</v>
+      </c>
+      <c r="L31" s="3">
+        <v>46260.0</v>
       </c>
       <c r="M31" s="3">
-        <v>46196.0</v>
+        <v>46109.0</v>
       </c>
       <c r="N31" s="3">
-        <v>46196.0</v>
+        <v>46109.0</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="P31" s="1">
-        <v>970.0</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0.0</v>
       </c>
       <c r="R31" s="1">
         <v>0.0</v>
       </c>
       <c r="S31" s="1">
-        <v>266.0</v>
+        <v>631.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="U31" s="1">
-        <v>330.0</v>
+        <v>1049.0</v>
       </c>
       <c r="V31" s="1">
         <v>0.0</v>
       </c>
       <c r="W31" s="4">
-        <v>76.0</v>
+        <v>176.0</v>
       </c>
       <c r="X31" s="3">
-        <v>46291.0</v>
+        <v>46140.0</v>
       </c>
       <c r="Y31" s="1">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
       <c r="Z31" s="3">
-        <v>46074.0</v>
+        <v>46223.0</v>
       </c>
       <c r="AA31" s="3">
-        <v>46231.0</v>
-      </c>
-      <c r="AB31" s="6">
-        <v>46094.0</v>
+        <v>46111.0</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="AC31" s="5" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="AD31" s="1">
-        <v>694.0</v>
+        <v>696.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>46084.354166666664</v>
+        <v>46089.354166666664</v>
       </c>
       <c r="B32" s="3">
-        <v>46224.0</v>
+        <v>46107.0</v>
       </c>
       <c r="C32" s="3">
-        <v>46286.0</v>
+        <v>46199.0</v>
       </c>
       <c r="D32" s="3">
-        <v>46194.0</v>
+        <v>46107.0</v>
       </c>
       <c r="E32" s="1">
-        <v>97.0</v>
+        <v>72.0</v>
       </c>
       <c r="F32" s="3">
-        <v>46074.0</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>36</v>
+        <v>46285.0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>46205.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="J32" s="3">
-        <v>46235.0</v>
+        <v>46087.0</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="L32" s="3">
-        <v>46224.0</v>
+        <v>46107.0</v>
       </c>
       <c r="M32" s="3">
-        <v>46135.0</v>
+        <v>46292.0</v>
       </c>
       <c r="N32" s="3">
-        <v>46135.0</v>
+        <v>46292.0</v>
       </c>
       <c r="O32" s="1">
         <v>0.0</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="1">
         <v>0.0</v>
@@ -3674,274 +3632,274 @@
         <v>0.0</v>
       </c>
       <c r="S32" s="1">
-        <v>200.0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>46181.0</v>
+        <v>690.0</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="U32" s="1">
-        <v>218.0</v>
+        <v>874.0</v>
       </c>
       <c r="V32" s="1">
         <v>0.0</v>
       </c>
       <c r="W32" s="4">
-        <v>71.0</v>
+        <v>167.0</v>
       </c>
       <c r="X32" s="3">
-        <v>46229.0</v>
+        <v>46109.0</v>
       </c>
       <c r="Y32" s="1">
-        <v>72.0</v>
+        <v>63.0</v>
       </c>
       <c r="Z32" s="3">
-        <v>46102.0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>46140.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="AD32" s="1">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>46084.333333333336</v>
+        <v>46089.333333333336</v>
       </c>
       <c r="B33" s="3">
-        <v>46194.0</v>
+        <v>46106.0</v>
       </c>
       <c r="C33" s="3">
-        <v>46224.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D33" s="3">
-        <v>46133.0</v>
+        <v>46258.0</v>
       </c>
       <c r="E33" s="1">
-        <v>97.0</v>
+        <v>73.0</v>
       </c>
       <c r="F33" s="3">
-        <v>46043.0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>30</v>
+        <v>46042.0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>46205.0</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J33" s="3">
+        <v>46239.0</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33" s="3">
+        <v>46106.0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>46199.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>46199.0</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>625.0</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="U33" s="1">
+        <v>889.0</v>
+      </c>
+      <c r="V33" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W33" s="4">
+        <v>146.0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>46261.0</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>46232.0</v>
+      </c>
+      <c r="AB33" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L33" s="3">
-        <v>46194.0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>46104.0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>46104.0</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>167.0</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="U33" s="1">
-        <v>185.0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W33" s="4">
-        <v>67.0</v>
-      </c>
-      <c r="X33" s="3">
-        <v>46199.0</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>46043.0</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>46081.0</v>
-      </c>
-      <c r="AB33" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC33" s="5" t="s">
-        <v>143</v>
+      <c r="AC33" s="4">
+        <v>1095.0</v>
       </c>
       <c r="AD33" s="1">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>46084.3125</v>
+        <v>46089.3125</v>
       </c>
       <c r="B34" s="3">
-        <v>46102.0</v>
+        <v>46258.0</v>
       </c>
       <c r="C34" s="3">
-        <v>46133.0</v>
+        <v>46078.0</v>
       </c>
       <c r="D34" s="3">
-        <v>46074.0</v>
+        <v>46136.0</v>
       </c>
       <c r="E34" s="1">
-        <v>97.0</v>
+        <v>78.0</v>
       </c>
       <c r="F34" s="3">
-        <v>46254.0</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>30</v>
+        <v>46223.0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>46205.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="J34" s="3">
-        <v>46082.0</v>
+        <v>46239.0</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="L34" s="3">
-        <v>46102.0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>23.0</v>
+        <v>46258.0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>46138.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>46138.0</v>
       </c>
       <c r="O34" s="1">
         <v>0.0</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>136</v>
+      <c r="P34" s="1">
+        <v>970.0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0.0</v>
       </c>
       <c r="R34" s="1">
         <v>0.0</v>
       </c>
       <c r="S34" s="1">
-        <v>130.0</v>
+        <v>424.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="U34" s="1">
-        <v>142.0</v>
+        <v>759.0</v>
       </c>
       <c r="V34" s="1">
         <v>0.0</v>
       </c>
       <c r="W34" s="4">
-        <v>63.0</v>
+        <v>135.0</v>
       </c>
       <c r="X34" s="3">
-        <v>46168.0</v>
+        <v>46200.0</v>
       </c>
       <c r="Y34" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>21.0</v>
+        <v>66.0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>46193.0</v>
       </c>
       <c r="AA34" s="3">
-        <v>46050.0</v>
+        <v>46110.0</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="AC34" s="5" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="AD34" s="1">
-        <v>695.0</v>
+        <v>697.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>46084.291666666664</v>
-      </c>
-      <c r="B35" s="1">
-        <v>21.0</v>
+        <v>46089.291666666664</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46046.0</v>
       </c>
       <c r="C35" s="3">
-        <v>46074.0</v>
+        <v>46136.0</v>
       </c>
       <c r="D35" s="3">
-        <v>46254.0</v>
+        <v>46135.0</v>
       </c>
       <c r="E35" s="1">
-        <v>97.0</v>
+        <v>80.0</v>
       </c>
       <c r="F35" s="3">
-        <v>46162.0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.0</v>
+        <v>46132.0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>46205.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0.0</v>
+        <v>53</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J35" s="3">
-        <v>46082.0</v>
+        <v>46209.0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L35" s="1">
-        <v>21.0</v>
+        <v>102</v>
+      </c>
+      <c r="L35" s="3">
+        <v>46046.0</v>
       </c>
       <c r="M35" s="3">
-        <v>46195.0</v>
+        <v>46167.0</v>
       </c>
       <c r="N35" s="3">
-        <v>46195.0</v>
+        <v>46167.0</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>148</v>
+        <v>135</v>
+      </c>
+      <c r="P35" s="1">
+        <v>970.0</v>
       </c>
       <c r="Q35" s="1">
         <v>0.0</v>
@@ -3950,129 +3908,129 @@
         <v>0.0</v>
       </c>
       <c r="S35" s="1">
-        <v>97.0</v>
+        <v>450.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="U35" s="1">
-        <v>121.0</v>
+        <v>617.0</v>
       </c>
       <c r="V35" s="1">
         <v>0.0</v>
       </c>
       <c r="W35" s="4">
-        <v>56.0</v>
+        <v>119.0</v>
       </c>
       <c r="X35" s="3">
-        <v>46107.0</v>
+        <v>46080.0</v>
       </c>
       <c r="Y35" s="1">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
       <c r="Z35" s="3">
-        <v>46285.0</v>
+        <v>46101.0</v>
       </c>
       <c r="AA35" s="3">
-        <v>46292.0</v>
+        <v>46231.0</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="AC35" s="5" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="AD35" s="1">
-        <v>692.0</v>
+        <v>689.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>46084.270833333336</v>
+        <v>46089.270833333336</v>
       </c>
       <c r="B36" s="3">
-        <v>46254.0</v>
+        <v>46256.0</v>
       </c>
       <c r="C36" s="3">
-        <v>46254.0</v>
+        <v>46104.0</v>
       </c>
       <c r="D36" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>46132.0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>46055.0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I36" s="6">
+        <v>46057.0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>46239.0</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L36" s="3">
+        <v>46256.0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>46046.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>46046.0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S36" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="U36" s="1">
+        <v>452.0</v>
+      </c>
+      <c r="V36" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W36" s="4">
+        <v>94.0</v>
+      </c>
+      <c r="X36" s="3">
+        <v>46291.0</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="Z36" s="3">
         <v>46223.0</v>
       </c>
-      <c r="E36" s="1">
-        <v>97.0</v>
-      </c>
-      <c r="F36" s="3">
-        <v>46101.0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L36" s="3">
-        <v>46254.0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="N36" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="R36" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="U36" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W36" s="4">
-        <v>51.0</v>
-      </c>
-      <c r="X36" s="3">
-        <v>46079.0</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>21.0</v>
-      </c>
       <c r="AA36" s="3">
-        <v>46261.0</v>
+        <v>46140.0</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="AC36" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AD36" s="1">
         <v>696.0</v>
@@ -4080,334 +4038,334 @@
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>46084.25</v>
+        <v>46089.25</v>
       </c>
       <c r="B37" s="3">
-        <v>46254.0</v>
+        <v>46103.0</v>
       </c>
       <c r="C37" s="3">
-        <v>46254.0</v>
+        <v>46195.0</v>
       </c>
       <c r="D37" s="3">
-        <v>46254.0</v>
+        <v>46075.0</v>
       </c>
       <c r="E37" s="1">
-        <v>96.0</v>
+        <v>91.0</v>
       </c>
       <c r="F37" s="3">
-        <v>46042.0</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>36</v>
+        <v>46223.0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>46082.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J37" s="3">
-        <v>46055.0</v>
+        <v>46025.0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="L37" s="3">
-        <v>46254.0</v>
+        <v>46103.0</v>
       </c>
       <c r="M37" s="3">
-        <v>46075.0</v>
+        <v>46196.0</v>
       </c>
       <c r="N37" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0.0</v>
+        <v>46196.0</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" s="3">
-        <v>46175.0</v>
+        <v>142</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0.0</v>
       </c>
       <c r="S37" s="1">
-        <v>2.0</v>
+        <v>99.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="U37" s="1">
-        <v>11.0</v>
+        <v>171.0</v>
       </c>
       <c r="V37" s="1">
         <v>0.0</v>
       </c>
       <c r="W37" s="4">
-        <v>51.0</v>
+        <v>82.0</v>
       </c>
       <c r="X37" s="3">
-        <v>46079.0</v>
+        <v>46229.0</v>
       </c>
       <c r="Y37" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="Z37" s="1">
-        <v>21.0</v>
+        <v>69.0</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>46193.0</v>
       </c>
       <c r="AA37" s="3">
-        <v>46261.0</v>
+        <v>46081.0</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="AC37" s="5" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="AD37" s="1">
-        <v>692.0</v>
+        <v>691.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>46084.229166666664</v>
+        <v>46089.229166666664</v>
       </c>
       <c r="B38" s="3">
-        <v>46254.0</v>
+        <v>46286.0</v>
       </c>
       <c r="C38" s="3">
-        <v>46254.0</v>
+        <v>46075.0</v>
       </c>
       <c r="D38" s="3">
-        <v>46254.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E38" s="1">
-        <v>96.0</v>
+        <v>91.0</v>
       </c>
       <c r="F38" s="3">
-        <v>46073.0</v>
-      </c>
-      <c r="G38" s="3">
-        <v>46082.0</v>
+        <v>46132.0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J38" s="3">
-        <v>46146.0</v>
+        <v>46205.0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="L38" s="3">
-        <v>46254.0</v>
+        <v>46286.0</v>
       </c>
       <c r="M38" s="3">
-        <v>46103.0</v>
+        <v>46076.0</v>
       </c>
       <c r="N38" s="3">
-        <v>46103.0</v>
+        <v>46076.0</v>
       </c>
       <c r="O38" s="1">
         <v>0.0</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>46113.0</v>
-      </c>
-      <c r="R38" s="3">
-        <v>46115.0</v>
+        <v>109</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0.0</v>
       </c>
       <c r="S38" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0.0</v>
+        <v>45.0</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="U38" s="1">
-        <v>0.0</v>
+        <v>77.0</v>
       </c>
       <c r="V38" s="1">
         <v>0.0</v>
       </c>
       <c r="W38" s="4">
-        <v>52.0</v>
+        <v>74.0</v>
       </c>
       <c r="X38" s="3">
-        <v>46107.0</v>
+        <v>46168.0</v>
       </c>
       <c r="Y38" s="1">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="Z38" s="3">
-        <v>46043.0</v>
+        <v>46193.0</v>
       </c>
       <c r="AA38" s="3">
         <v>46292.0</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AC38" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="AD38" s="1">
-        <v>691.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>46084.208333333336</v>
+        <v>46089.208333333336</v>
       </c>
       <c r="B39" s="3">
-        <v>46285.0</v>
+        <v>46194.0</v>
       </c>
       <c r="C39" s="3">
-        <v>46285.0</v>
+        <v>46224.0</v>
       </c>
       <c r="D39" s="3">
-        <v>46254.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E39" s="1">
-        <v>96.0</v>
+        <v>92.0</v>
       </c>
       <c r="F39" s="3">
         <v>46073.0</v>
       </c>
-      <c r="G39" s="3">
-        <v>46082.0</v>
+      <c r="G39" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J39" s="3">
-        <v>46176.0</v>
+        <v>46205.0</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="L39" s="3">
-        <v>46285.0</v>
+        <v>46194.0</v>
       </c>
       <c r="M39" s="3">
-        <v>46103.0</v>
+        <v>46287.0</v>
       </c>
       <c r="N39" s="3">
-        <v>46103.0</v>
+        <v>46287.0</v>
       </c>
       <c r="O39" s="1">
         <v>0.0</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q39" s="3">
-        <v>46174.0</v>
-      </c>
-      <c r="R39" s="3">
-        <v>46117.0</v>
+        <v>149</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0.0</v>
       </c>
       <c r="S39" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="U39" s="1">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="V39" s="1">
         <v>0.0</v>
       </c>
       <c r="W39" s="4">
-        <v>53.0</v>
+        <v>67.0</v>
       </c>
       <c r="X39" s="3">
         <v>46138.0</v>
       </c>
       <c r="Y39" s="1">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="Z39" s="3">
-        <v>46074.0</v>
+        <v>46162.0</v>
       </c>
       <c r="AA39" s="3">
-        <v>46050.0</v>
+        <v>46261.0</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC39" s="4">
-        <v>1097.0</v>
+        <v>147</v>
+      </c>
+      <c r="AC39" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="AD39" s="1">
-        <v>692.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>46084.1875</v>
+        <v>46089.1875</v>
       </c>
       <c r="B40" s="3">
-        <v>46254.0</v>
+        <v>46255.0</v>
       </c>
       <c r="C40" s="3">
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="D40" s="3">
-        <v>46254.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E40" s="1">
-        <v>96.0</v>
+        <v>92.0</v>
       </c>
       <c r="F40" s="3">
-        <v>46073.0</v>
-      </c>
-      <c r="G40" s="3">
-        <v>46082.0</v>
+        <v>46132.0</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J40" s="1">
-        <v>4.0</v>
+        <v>61</v>
+      </c>
+      <c r="J40" s="3">
+        <v>46176.0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="L40" s="3">
-        <v>46254.0</v>
+        <v>46255.0</v>
       </c>
       <c r="M40" s="3">
-        <v>46103.0</v>
+        <v>46045.0</v>
       </c>
       <c r="N40" s="3">
-        <v>46103.0</v>
+        <v>46045.0</v>
       </c>
       <c r="O40" s="1">
         <v>0.0</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>46055.0</v>
-      </c>
-      <c r="R40" s="3">
-        <v>46117.0</v>
+        <v>106</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0.0</v>
       </c>
       <c r="S40" s="1">
         <v>0.0</v>
@@ -4422,25 +4380,25 @@
         <v>0.0</v>
       </c>
       <c r="W40" s="4">
-        <v>52.0</v>
+        <v>72.0</v>
       </c>
       <c r="X40" s="3">
-        <v>46138.0</v>
+        <v>46199.0</v>
       </c>
       <c r="Y40" s="1">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="Z40" s="3">
-        <v>46074.0</v>
-      </c>
-      <c r="AA40" s="3">
-        <v>46050.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>28.0</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="AC40" s="5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="AD40" s="1">
         <v>697.0</v>
@@ -4448,150 +4406,150 @@
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>46084.166666666664</v>
+        <v>46089.166666666664</v>
       </c>
       <c r="B41" s="3">
-        <v>46254.0</v>
-      </c>
-      <c r="C41" s="3">
-        <v>46254.0</v>
+        <v>46286.0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>22.0</v>
       </c>
       <c r="D41" s="3">
+        <v>46286.0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>46132.0</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J41" s="3">
+        <v>46205.0</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L41" s="3">
+        <v>46286.0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>46076.0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>46076.0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W41" s="4">
+        <v>75.0</v>
+      </c>
+      <c r="X41" s="3">
+        <v>46229.0</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>46223.0</v>
       </c>
-      <c r="E41" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="F41" s="3">
-        <v>46042.0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>46235.0</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J41" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L41" s="3">
-        <v>46254.0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="N41" s="3">
-        <v>46075.0</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>46180.0</v>
-      </c>
-      <c r="S41" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T41" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="U41" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W41" s="4">
-        <v>51.0</v>
-      </c>
-      <c r="X41" s="3">
-        <v>46199.0</v>
-      </c>
-      <c r="Y41" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>46102.0</v>
-      </c>
       <c r="AA41" s="3">
-        <v>46109.0</v>
+        <v>46081.0</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="AC41" s="5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AD41" s="1">
-        <v>693.0</v>
+        <v>696.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>46084.145833333336</v>
+        <v>46089.145833333336</v>
       </c>
       <c r="B42" s="3">
-        <v>46223.0</v>
+        <v>46075.0</v>
       </c>
       <c r="C42" s="3">
-        <v>46223.0</v>
-      </c>
-      <c r="D42" s="3">
+        <v>46103.0</v>
+      </c>
+      <c r="D42" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="F42" s="3">
         <v>46193.0</v>
       </c>
-      <c r="E42" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="F42" s="1">
-        <v>20.0</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J42" s="3">
-        <v>46055.0</v>
+        <v>46205.0</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="L42" s="3">
-        <v>46223.0</v>
+        <v>46075.0</v>
       </c>
       <c r="M42" s="3">
-        <v>46044.0</v>
+        <v>46135.0</v>
       </c>
       <c r="N42" s="3">
-        <v>46044.0</v>
+        <v>46135.0</v>
       </c>
       <c r="O42" s="1">
         <v>0.0</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>46114.0</v>
+        <v>155</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0.0</v>
       </c>
       <c r="R42" s="1">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="S42" s="1">
         <v>0.0</v>
@@ -4605,177 +4563,177 @@
       <c r="V42" s="1">
         <v>0.0</v>
       </c>
-      <c r="W42" s="4">
-        <v>49.0</v>
+      <c r="W42" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="X42" s="3">
-        <v>46199.0</v>
+        <v>46260.0</v>
       </c>
       <c r="Y42" s="1">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="Z42" s="3">
-        <v>46102.0</v>
+        <v>46285.0</v>
       </c>
       <c r="AA42" s="3">
-        <v>46109.0</v>
+        <v>46140.0</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AC42" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AD42" s="1">
-        <v>695.0</v>
+        <v>693.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>46084.125</v>
+        <v>46089.125</v>
       </c>
       <c r="B43" s="3">
-        <v>46193.0</v>
+        <v>46164.0</v>
       </c>
       <c r="C43" s="3">
-        <v>46193.0</v>
+        <v>46256.0</v>
       </c>
       <c r="D43" s="3">
-        <v>46193.0</v>
+        <v>46103.0</v>
       </c>
       <c r="E43" s="1">
-        <v>96.0</v>
+        <v>90.0</v>
       </c>
       <c r="F43" s="3">
-        <v>46284.0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>46055.0</v>
+        <v>46254.0</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I43" s="6">
-        <v>46057.0</v>
+        <v>95</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="J43" s="3">
-        <v>46117.0</v>
+        <v>46205.0</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="L43" s="3">
-        <v>46193.0</v>
+        <v>46164.0</v>
       </c>
       <c r="M43" s="3">
-        <v>46286.0</v>
+        <v>46257.0</v>
       </c>
       <c r="N43" s="3">
-        <v>46286.0</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0.0</v>
+        <v>46257.0</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="P43" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W43" s="4">
+        <v>87.0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>46291.0</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC43" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="Q43" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="T43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="U43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="V43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="W43" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>46199.0</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>46194.0</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>46170.0</v>
-      </c>
-      <c r="AB43" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="AC43" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="AD43" s="1">
-        <v>697.0</v>
+        <v>691.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>46084.104166666664</v>
-      </c>
-      <c r="B44" s="3">
-        <v>46163.0</v>
+        <v>46089.104166666664</v>
+      </c>
+      <c r="B44" s="1">
+        <v>23.0</v>
       </c>
       <c r="C44" s="3">
-        <v>46045.0</v>
+        <v>46076.0</v>
       </c>
       <c r="D44" s="3">
-        <v>46193.0</v>
+        <v>46256.0</v>
       </c>
       <c r="E44" s="1">
-        <v>96.0</v>
+        <v>88.0</v>
       </c>
       <c r="F44" s="3">
-        <v>46254.0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>46082.0</v>
+        <v>46285.0</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J44" s="3">
-        <v>46209.0</v>
+        <v>46025.0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L44" s="3">
-        <v>46163.0</v>
+        <v>95</v>
+      </c>
+      <c r="L44" s="1">
+        <v>23.0</v>
       </c>
       <c r="M44" s="3">
-        <v>46045.0</v>
+        <v>46105.0</v>
       </c>
       <c r="N44" s="3">
-        <v>46045.0</v>
+        <v>46105.0</v>
       </c>
       <c r="O44" s="1">
         <v>0.0</v>
       </c>
-      <c r="P44" s="1">
-        <v>968.0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>46247.0</v>
+      <c r="P44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0.0</v>
       </c>
       <c r="R44" s="1">
-        <v>62.0</v>
+        <v>0.0</v>
       </c>
       <c r="S44" s="1">
         <v>0.0</v>
@@ -4790,75 +4748,81 @@
         <v>0.0</v>
       </c>
       <c r="W44" s="4">
-        <v>66.0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>46291.0</v>
+        <v>97.0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>27.0</v>
       </c>
       <c r="Y44" s="1">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="Z44" s="3">
-        <v>46194.0</v>
+        <v>46043.0</v>
       </c>
       <c r="AA44" s="3">
-        <v>46262.0</v>
+        <v>46231.0</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AC44" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AD44" s="1">
-        <v>690.0</v>
+        <v>693.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>46084.083333333336</v>
+        <v>46089.083333333336</v>
       </c>
       <c r="B45" s="3">
+        <v>46045.0</v>
+      </c>
+      <c r="C45" s="3">
         <v>46076.0</v>
       </c>
-      <c r="C45" s="3">
-        <v>46104.0</v>
-      </c>
-      <c r="D45" s="3">
+      <c r="D45" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J45" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L45" s="3">
         <v>46045.0</v>
       </c>
-      <c r="E45" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>46164.0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>46076.0</v>
-      </c>
       <c r="M45" s="3">
-        <v>46289.0</v>
+        <v>46136.0</v>
       </c>
       <c r="N45" s="3">
-        <v>46289.0</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>968.0</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>30</v>
+        <v>46136.0</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0.0</v>
       </c>
       <c r="R45" s="1">
         <v>0.0</v>
@@ -4875,73 +4839,79 @@
       <c r="V45" s="1">
         <v>0.0</v>
       </c>
-      <c r="W45" s="4">
-        <v>101.0</v>
+      <c r="W45" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="X45" s="3">
         <v>46049.0</v>
       </c>
       <c r="Y45" s="1">
-        <v>75.0</v>
+        <v>69.0</v>
       </c>
       <c r="Z45" s="3">
-        <v>46075.0</v>
+        <v>46285.0</v>
       </c>
       <c r="AA45" s="3">
-        <v>46141.0</v>
+        <v>46231.0</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AC45" s="5" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="AD45" s="1">
-        <v>696.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>46084.0625</v>
+        <v>46089.0625</v>
       </c>
       <c r="B46" s="3">
-        <v>46135.0</v>
+        <v>46165.0</v>
       </c>
       <c r="C46" s="3">
-        <v>46165.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D46" s="3">
         <v>46104.0</v>
       </c>
       <c r="E46" s="1">
-        <v>96.0</v>
+        <v>84.0</v>
       </c>
       <c r="F46" s="3">
-        <v>46225.0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="L46" s="3">
-        <v>46135.0</v>
+        <v>46165.0</v>
       </c>
       <c r="M46" s="3">
-        <v>46078.0</v>
+        <v>46258.0</v>
       </c>
       <c r="N46" s="3">
-        <v>46078.0</v>
+        <v>46258.0</v>
       </c>
       <c r="O46" s="1">
         <v>0.0</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="Q46" s="1">
         <v>0.0</v>
@@ -4962,72 +4932,78 @@
         <v>0.0</v>
       </c>
       <c r="W46" s="4">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
       <c r="X46" s="3">
-        <v>46049.0</v>
+        <v>46080.0</v>
       </c>
       <c r="Y46" s="1">
-        <v>75.0</v>
+        <v>68.0</v>
       </c>
       <c r="Z46" s="3">
-        <v>46103.0</v>
+        <v>46223.0</v>
       </c>
       <c r="AA46" s="3">
-        <v>46141.0</v>
+        <v>46262.0</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AC46" s="5" t="s">
-        <v>41</v>
+        <v>168</v>
       </c>
       <c r="AD46" s="1">
-        <v>697.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>46084.041666666664</v>
+        <v>46089.041666666664</v>
       </c>
       <c r="B47" s="3">
-        <v>46135.0</v>
-      </c>
-      <c r="C47" s="3">
-        <v>46165.0</v>
+        <v>46257.0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>24.0</v>
       </c>
       <c r="D47" s="3">
-        <v>46104.0</v>
+        <v>46226.0</v>
       </c>
       <c r="E47" s="1">
-        <v>96.0</v>
+        <v>82.0</v>
       </c>
       <c r="F47" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>0.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>46082.0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="L47" s="3">
-        <v>46135.0</v>
+        <v>46257.0</v>
       </c>
       <c r="M47" s="3">
-        <v>46078.0</v>
+        <v>46106.0</v>
       </c>
       <c r="N47" s="3">
-        <v>46078.0</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0.0</v>
+        <v>46106.0</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="Q47" s="1">
         <v>0.0</v>
@@ -5048,25 +5024,25 @@
         <v>0.0</v>
       </c>
       <c r="W47" s="4">
-        <v>106.0</v>
+        <v>115.0</v>
       </c>
       <c r="X47" s="3">
-        <v>46080.0</v>
+        <v>46108.0</v>
       </c>
       <c r="Y47" s="1">
-        <v>75.0</v>
+        <v>67.0</v>
       </c>
       <c r="Z47" s="3">
-        <v>46103.0</v>
+        <v>46193.0</v>
       </c>
       <c r="AA47" s="3">
-        <v>46202.0</v>
+        <v>46293.0</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC47" s="5" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="AD47" s="1">
         <v>697.0</v>
@@ -5074,46 +5050,52 @@
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>46084.020833333336</v>
+        <v>46089.020833333336</v>
       </c>
       <c r="B48" s="3">
-        <v>46104.0</v>
+        <v>46046.0</v>
       </c>
       <c r="C48" s="3">
-        <v>46135.0</v>
-      </c>
-      <c r="D48" s="3">
-        <v>46104.0</v>
+        <v>46077.0</v>
+      </c>
+      <c r="D48" s="1">
+        <v>24.0</v>
       </c>
       <c r="E48" s="1">
-        <v>96.0</v>
+        <v>81.0</v>
       </c>
       <c r="F48" s="3">
-        <v>46225.0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0.0</v>
+        <v>46193.0</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J48" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="L48" s="3">
-        <v>46104.0</v>
+        <v>46046.0</v>
       </c>
       <c r="M48" s="3">
-        <v>46047.0</v>
+        <v>46198.0</v>
       </c>
       <c r="N48" s="3">
-        <v>46047.0</v>
+        <v>46198.0</v>
       </c>
       <c r="O48" s="1">
         <v>0.0</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="Q48" s="1">
         <v>0.0</v>
@@ -5134,72 +5116,78 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="4">
-        <v>104.0</v>
+        <v>119.0</v>
       </c>
       <c r="X48" s="3">
-        <v>46080.0</v>
+        <v>46139.0</v>
       </c>
       <c r="Y48" s="1">
-        <v>75.0</v>
+        <v>67.0</v>
       </c>
       <c r="Z48" s="3">
-        <v>46103.0</v>
+        <v>46223.0</v>
       </c>
       <c r="AA48" s="3">
-        <v>46202.0</v>
-      </c>
-      <c r="AB48" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AC48" s="4">
-        <v>1092.0</v>
+        <v>46051.0</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>46368.0</v>
+      </c>
+      <c r="AC48" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="AD48" s="1">
-        <v>690.0</v>
+        <v>693.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>46084.0</v>
+        <v>46089.0</v>
       </c>
       <c r="B49" s="3">
-        <v>46165.0</v>
+        <v>46105.0</v>
       </c>
       <c r="C49" s="3">
-        <v>46165.0</v>
+        <v>46166.0</v>
       </c>
       <c r="D49" s="3">
-        <v>46135.0</v>
+        <v>46077.0</v>
       </c>
       <c r="E49" s="1">
-        <v>96.0</v>
+        <v>80.0</v>
       </c>
       <c r="F49" s="3">
-        <v>46256.0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0.0</v>
+        <v>46223.0</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="L49" s="3">
-        <v>46165.0</v>
+        <v>46105.0</v>
       </c>
       <c r="M49" s="3">
-        <v>46106.0</v>
+        <v>46290.0</v>
       </c>
       <c r="N49" s="3">
-        <v>46106.0</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>968.0</v>
+        <v>46290.0</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="Q49" s="1">
         <v>0.0</v>
@@ -5220,28 +5208,28 @@
         <v>0.0</v>
       </c>
       <c r="W49" s="4">
-        <v>108.0</v>
+        <v>125.0</v>
       </c>
       <c r="X49" s="3">
-        <v>46080.0</v>
+        <v>46139.0</v>
       </c>
       <c r="Y49" s="1">
-        <v>75.0</v>
+        <v>67.0</v>
       </c>
       <c r="Z49" s="3">
-        <v>46103.0</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>46202.0</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>171</v>
+        <v>46254.0</v>
+      </c>
+      <c r="AA49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>46368.0</v>
       </c>
       <c r="AC49" s="5" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="AD49" s="1">
-        <v>696.0</v>
+        <v>692.0</v>
       </c>
     </row>
   </sheetData>
